--- a/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
+++ b/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">1. Population</t>
   </si>
   <si>
-    <t xml:space="preserve">Mid-year population, thousands, present-day borders, 1913 and 1919-2022</t>
+    <t xml:space="preserve">Mid-year population, thousands, 1913 and 1919-2022 (borders of the republic to 1944, present-day borders thereafter)</t>
   </si>
   <si>
     <t xml:space="preserve">2. Sectoral indices</t>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">4. Benchmarks</t>
   </si>
   <si>
-    <t xml:space="preserve">1938 and 1990 benchmark GDP by sector at current prices</t>
+    <t xml:space="preserve">1938 and 1990 benchmark GDP by sector at current prices (taxes and totals as in Table 1)</t>
   </si>
   <si>
     <t xml:space="preserve">5. Overlaps</t>
@@ -83,6 +83,24 @@
   </si>
   <si>
     <t xml:space="preserve">Int$2011 = Int$1990 x 1.594, compatible with the Maddison Project Database (version 2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scripts/R/tables.R (repository: latvia-estonia-gdp-paper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R version 4.5.0 (2025-04-11 ucrt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
   </si>
   <si>
     <t xml:space="preserve">Year</t>
@@ -200,6 +218,18 @@
   </si>
   <si>
     <t xml:space="preserve">Public administration, defence, education &amp; health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross value-added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxes less subsidies on products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP at market prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP per capita, national currency (kroon / roubles)</t>
   </si>
   <si>
     <t xml:space="preserve">Splice</t>
@@ -691,6 +721,38 @@
         <v>21</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -736,10 +798,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -1627,85 +1689,85 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="O1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="P1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="S1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="T1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="U1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="V1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="W1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="X1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="Y1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="Z1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AA1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
@@ -7582,13 +7644,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
@@ -8791,24 +8853,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B2" t="n">
         <v>250.1</v>
@@ -8825,7 +8887,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B3" t="n">
         <v>132.1</v>
@@ -8842,7 +8904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -8859,7 +8921,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B5" t="n">
         <v>32.2</v>
@@ -8876,7 +8938,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B6" t="n">
         <v>120.5</v>
@@ -8893,7 +8955,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B7" t="n">
         <v>99.3</v>
@@ -8910,7 +8972,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>5.5</v>
@@ -8924,6 +8986,60 @@
       <c r="E8" t="n">
         <v>2.6</v>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="n">
+        <v>653.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7384.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="n">
+        <v>670.9</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" t="n">
+        <v>7384.1</v>
+      </c>
+      <c r="E11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="n">
+        <v>592.384473328351</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12" t="n">
+        <v>4705.72415806023</v>
+      </c>
+      <c r="E12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8970,22 +9086,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -9005,7 +9121,7 @@
         <v>-1.6</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -9025,7 +9141,7 @@
         <v>3.6</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -9045,7 +9161,7 @@
         <v>-3</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -9065,7 +9181,7 @@
         <v>-0.3</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -9085,7 +9201,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -9105,7 +9221,7 @@
         <v>-0.7</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -9125,7 +9241,7 @@
         <v>-12.4</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -9145,7 +9261,7 @@
         <v>-19.4</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -9165,7 +9281,7 @@
         <v>-18.6</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -9185,7 +9301,7 @@
         <v>-25.8</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
+++ b/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
@@ -9212,13 +9212,13 @@
         <v>1991</v>
       </c>
       <c r="C7" t="n">
-        <v>7505.5</v>
+        <v>7503.6</v>
       </c>
       <c r="D7" t="n">
-        <v>7558</v>
+        <v>7560</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F7" t="s">
         <v>76</v>
@@ -9232,13 +9232,13 @@
         <v>1991</v>
       </c>
       <c r="C8" t="n">
-        <v>5399.8</v>
+        <v>5313.9</v>
       </c>
       <c r="D8" t="n">
         <v>6069.3</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.4</v>
+        <v>-14.2</v>
       </c>
       <c r="F8" t="s">
         <v>77</v>
@@ -9252,13 +9252,13 @@
         <v>1991</v>
       </c>
       <c r="C9" t="n">
-        <v>4916.3</v>
+        <v>4732.7</v>
       </c>
       <c r="D9" t="n">
         <v>5870.1</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.4</v>
+        <v>-24</v>
       </c>
       <c r="F9" t="s">
         <v>78</v>
@@ -9272,13 +9272,13 @@
         <v>1991</v>
       </c>
       <c r="C10" t="n">
-        <v>4973.4</v>
+        <v>4799.3</v>
       </c>
       <c r="D10" t="n">
         <v>5898.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-18.6</v>
+        <v>-22.9</v>
       </c>
       <c r="F10" t="s">
         <v>78</v>
@@ -9292,13 +9292,13 @@
         <v>1991</v>
       </c>
       <c r="C11" t="n">
-        <v>4989.3</v>
+        <v>4657.3</v>
       </c>
       <c r="D11" t="n">
         <v>6276.6</v>
       </c>
       <c r="E11" t="n">
-        <v>-25.8</v>
+        <v>-34.8</v>
       </c>
       <c r="F11" t="s">
         <v>79</v>

--- a/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
+++ b/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Generated on</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-16</t>
+    <t xml:space="preserve">2026-10-17</t>
   </si>
   <si>
     <t xml:space="preserve">Year</t>

--- a/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
+++ b/Paper/estonia/supplementary/Estonia_online_data_appendix.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Generated on</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-17</t>
+    <t xml:space="preserve">2026-10-22</t>
   </si>
   <si>
     <t xml:space="preserve">Year</t>
